--- a/Result/profitability/3374.xlsx
+++ b/Result/profitability/3374.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM63"/>
+  <dimension ref="A1:AM64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>1.23</v>
+        <v>1.15375</v>
       </c>
       <c r="N2" t="n">
-        <v>26.9225</v>
+        <v>25.4025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.21</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1225</v>
+        <v>1.09375</v>
       </c>
       <c r="N3" t="n">
-        <v>24.7525</v>
+        <v>23.89875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.72375</v>
+        <v>0.7487499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>14.97375</v>
+        <v>14.715</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7587499999999999</v>
+        <v>0.91125</v>
       </c>
       <c r="N5" t="n">
-        <v>14.6825</v>
+        <v>16.18875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>0.89625</v>
+        <v>0.8799999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>15.95</v>
+        <v>15.77625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.89</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8087499999999999</v>
+        <v>0.7549999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>14.9</v>
+        <v>14.255</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8429,6 +8429,133 @@
       </c>
       <c r="AM63" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1580</v>
+      </c>
+      <c r="E64" t="n">
+        <v>604</v>
+      </c>
+      <c r="F64" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="G64" t="n">
+        <v>487</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>22.27%</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>487</v>
+      </c>
+      <c r="K64" t="n">
+        <v>396</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.4525</v>
+      </c>
+      <c r="N64" t="n">
+        <v>29.855</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.04000000000000004</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0.028169014084507</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>-0.06743088334457181</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>5.083333333333333</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0.7719410634208841</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
